--- a/전기요금완료본.xlsx
+++ b/전기요금완료본.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01. 녹색에너지전략연구소\0. 2026\0. TARA WP3\칼큘레이터\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5347D257-BBB2-4C25-99B7-5FE46818A838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48B0BDDA-3FD4-4BD8-82B0-6854E34ECB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{3788E499-6229-45B0-A3ED-4B24EF3FABB3}">
+    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{3788E499-6229-45B0-A3ED-4B24EF3FABB3}">
       <text>
         <t>[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -720,8 +720,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="474">
   <si>
     <t>INPUT</t>
   </si>
@@ -863,36 +885,6 @@
   </si>
   <si>
     <t>난방기기(선택)</t>
-  </si>
-  <si>
-    <t>콘덴싱 가스보일러</t>
-  </si>
-  <si>
-    <t>일반 가스보일러</t>
-  </si>
-  <si>
-    <t>기름보일러</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>LPG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>보일러</t>
-    </r>
   </si>
   <si>
     <t>기기 효율</t>
@@ -4278,6 +4270,37 @@
     <t>연차</t>
     <phoneticPr fontId="52" type="noConversion"/>
   </si>
+  <si>
+    <t>도시가스</t>
+    <phoneticPr fontId="52" type="noConversion"/>
+  </si>
+  <si>
+    <t>LPG</t>
+    <phoneticPr fontId="52" type="noConversion"/>
+  </si>
+  <si>
+    <t>인덕션(전기)</t>
+    <phoneticPr fontId="52" type="noConversion"/>
+  </si>
+  <si>
+    <t>가스 일반보일러</t>
+    <phoneticPr fontId="52" type="noConversion"/>
+  </si>
+  <si>
+    <t>등유 보일러</t>
+    <phoneticPr fontId="52" type="noConversion"/>
+  </si>
+  <si>
+    <t>LPG 보일러</t>
+    <phoneticPr fontId="52" type="noConversion"/>
+  </si>
+  <si>
+    <t>가스 콘덴싱보일러</t>
+  </si>
+  <si>
+    <t>가스 콘덴싱보일러</t>
+    <phoneticPr fontId="52" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -4304,7 +4327,7 @@
     <numFmt numFmtId="191" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="192" formatCode="0_ "/>
   </numFmts>
-  <fonts count="65">
+  <fonts count="64">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4728,13 +4751,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -5131,7 +5147,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5598,23 +5614,20 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="0" xfId="5" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="5" fillId="5" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="182" fontId="63" fillId="5" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="182" fontId="62" fillId="5" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="4" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="4" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="4" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
@@ -5638,18 +5651,6 @@
     <xf numFmtId="186" fontId="32" fillId="14" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="45" fillId="17" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5657,6 +5658,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="19" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11862,7 +11875,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H10" dT="2026-05-04T07:11:54.99" personId="{648F1D77-FDA2-480D-8205-3681E32C4F85}" id="{3788E499-6229-45B0-A3ED-4B24EF3FABB3}">
+  <threadedComment ref="J10" dT="2026-05-04T07:11:54.99" personId="{648F1D77-FDA2-480D-8205-3681E32C4F85}" id="{3788E499-6229-45B0-A3ED-4B24EF3FABB3}">
     <text>제11차 전기본 온실가스 배출목표(백만톤)/전력계통소비량(TWh)</text>
   </threadedComment>
 </ThreadedComments>
@@ -11870,7 +11883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:Q89"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="25.875" style="1" customWidth="1"/>
@@ -11883,12 +11896,12 @@
     <col min="14" max="15" width="9.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="2:17">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:8">
+    <row r="2" spans="2:17">
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -11896,7 +11909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:8">
+    <row r="3" spans="2:17">
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
@@ -11907,7 +11920,7 @@
       <c r="E3"/>
       <c r="F3"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:17">
       <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
@@ -11919,7 +11932,7 @@
       <c r="E4"/>
       <c r="F4"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:17">
       <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
@@ -11931,7 +11944,7 @@
       <c r="E5"/>
       <c r="F5"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:17">
       <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
@@ -11939,112 +11952,127 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:17">
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="E8" t="s">
+        <v>473</v>
+      </c>
+      <c r="F8" t="s">
+        <v>469</v>
+      </c>
+      <c r="G8" t="s">
+        <v>470</v>
+      </c>
+      <c r="H8" t="s">
+        <v>471</v>
+      </c>
+      <c r="I8" t="s">
+        <v>460</v>
+      </c>
+      <c r="J8" t="s">
+        <v>462</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+    </row>
+    <row r="9" spans="2:17">
+      <c r="B9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="166" t="s">
-        <v>464</v>
-      </c>
-      <c r="H8" s="166" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="10">
+      <c r="E9" s="10">
         <v>0.92</v>
       </c>
-      <c r="D9" s="10">
+      <c r="F9" s="10">
         <v>0.83</v>
       </c>
-      <c r="E9" s="10">
+      <c r="G9" s="10">
         <v>0.82</v>
       </c>
-      <c r="F9" s="10">
+      <c r="H9" s="10">
         <v>0.9</v>
       </c>
-      <c r="G9" s="10">
+      <c r="I9" s="10">
         <f>O50*100%</f>
         <v>3.1799323891634077</v>
       </c>
-      <c r="H9" s="10">
+      <c r="J9" s="10">
         <f>O50*100%</f>
         <v>3.1799323891634077</v>
       </c>
-    </row>
-    <row r="10" spans="2:8">
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+    </row>
+    <row r="10" spans="2:17">
       <c r="B10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="11">
+        <v>10</v>
+      </c>
+      <c r="E10" s="11">
         <v>0.21847826086956501</v>
       </c>
-      <c r="D10" s="11">
+      <c r="F10" s="11">
         <v>0.24216867469879499</v>
       </c>
-      <c r="E10" s="11">
+      <c r="G10" s="11">
         <v>0.30634828188701202</v>
       </c>
-      <c r="F10" s="11">
+      <c r="H10" s="11">
         <v>0.25555555555555598</v>
       </c>
-      <c r="G10" s="11">
-        <f>0.4173/G9</f>
+      <c r="I10" s="11">
+        <f>0.4173/I9</f>
         <v>0.13122920519382028</v>
       </c>
-      <c r="H10" s="12">
-        <f>(83.1/624.5)/H9</f>
+      <c r="J10" s="12">
+        <f>(83.1/624.5)/J9</f>
         <v>4.1845686284398581E-2</v>
       </c>
-    </row>
-    <row r="11" spans="2:8">
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" spans="2:17">
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="2:8">
+    <row r="12" spans="2:17">
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:17">
       <c r="B13" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D13"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="2:8">
+      <c r="E13" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17">
       <c r="B14" s="9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C14" s="124">
         <f>IF(OR(TRIM(C13)="도시가스",TRIM(C13)="LPG"),84.75%,100%)</f>
@@ -12052,61 +12080,61 @@
       </c>
       <c r="D14" s="14"/>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15" spans="2:17">
       <c r="C15" s="15"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:17">
       <c r="B16" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
         <v>22</v>
       </c>
-      <c r="D17" t="s">
+      <c r="H17" t="s">
         <v>23</v>
       </c>
-      <c r="E17" t="s">
+      <c r="I17" t="s">
         <v>24</v>
       </c>
-      <c r="F17" t="s">
+      <c r="J17" t="s">
         <v>25</v>
       </c>
-      <c r="G17" t="s">
+      <c r="K17" t="s">
         <v>26</v>
       </c>
-      <c r="H17" t="s">
+      <c r="L17" t="s">
         <v>27</v>
       </c>
-      <c r="I17" t="s">
+      <c r="M17" t="s">
         <v>28</v>
       </c>
-      <c r="J17" t="s">
+      <c r="N17" t="s">
         <v>29</v>
       </c>
-      <c r="K17" t="s">
+      <c r="O17" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="L17" t="s">
-        <v>31</v>
-      </c>
-      <c r="M17" t="s">
-        <v>32</v>
-      </c>
-      <c r="N17" t="s">
-        <v>33</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="B18" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C18" s="16">
         <v>126616.00749781499</v>
@@ -12162,21 +12190,21 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="B20" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C20" s="19">
         <f>_xlfn.XLOOKUP($B$19, Sheet3!$A$2:$A$19, Sheet3!C$2:C$19, "")</f>
@@ -12244,53 +12272,53 @@
     </row>
     <row r="22" spans="1:15">
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
+      <c r="H23" t="s">
         <v>23</v>
       </c>
-      <c r="E23" t="s">
+      <c r="I23" t="s">
         <v>24</v>
       </c>
-      <c r="F23" t="s">
+      <c r="J23" t="s">
         <v>25</v>
       </c>
-      <c r="G23" t="s">
+      <c r="K23" t="s">
         <v>26</v>
       </c>
-      <c r="H23" t="s">
+      <c r="L23" t="s">
         <v>27</v>
       </c>
-      <c r="I23" t="s">
+      <c r="M23" t="s">
         <v>28</v>
       </c>
-      <c r="J23" t="s">
+      <c r="N23" t="s">
         <v>29</v>
-      </c>
-      <c r="K23" t="s">
-        <v>30</v>
-      </c>
-      <c r="L23" t="s">
-        <v>31</v>
-      </c>
-      <c r="M23" t="s">
-        <v>32</v>
-      </c>
-      <c r="N23" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="B24" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C24" s="16">
         <v>305.87254901960802</v>
@@ -12346,7 +12374,7 @@
     </row>
     <row r="25" spans="1:15">
       <c r="B25" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C25" s="22">
         <v>8.6999999999999994E-2</v>
@@ -12402,10 +12430,10 @@
     </row>
     <row r="27" spans="1:15">
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
@@ -12418,15 +12446,15 @@
     </row>
     <row r="28" spans="1:15">
       <c r="B28" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="B29" s="131" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C29" s="8">
         <v>3</v>
@@ -12434,30 +12462,30 @@
     </row>
     <row r="32" spans="1:15">
       <c r="B32" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="2:14">
       <c r="B33" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="2:14">
       <c r="B34" s="2"/>
       <c r="C34" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G34" s="9"/>
     </row>
     <row r="35" spans="2:14">
       <c r="B35" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C35" s="25">
         <v>1000000</v>
@@ -12471,7 +12499,7 @@
     </row>
     <row r="36" spans="2:14">
       <c r="B36" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="26">
@@ -12483,7 +12511,7 @@
     </row>
     <row r="37" spans="2:14">
       <c r="B37" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C37" s="25"/>
       <c r="D37" s="25">
@@ -12501,25 +12529,25 @@
     </row>
     <row r="39" spans="2:14">
       <c r="B39" s="9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G39" s="27"/>
     </row>
     <row r="40" spans="2:14">
       <c r="B40" s="9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C40" s="28">
         <f>1250*1.1</f>
@@ -12539,7 +12567,7 @@
     </row>
     <row r="41" spans="2:14">
       <c r="B41" s="30" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C41" s="31">
         <f>22.3617*1.1</f>
@@ -12559,7 +12587,7 @@
     </row>
     <row r="42" spans="2:14" ht="17.25" customHeight="1">
       <c r="B42" s="9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C42" s="31">
         <f>C41*3.6</f>
@@ -12581,70 +12609,70 @@
     </row>
     <row r="43" spans="2:14" ht="17.25" customHeight="1">
       <c r="B43" s="32" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C43" s="33">
-        <f>(((O18-C40*12)/C42)*C14)*C9</f>
+        <f>(((O18-C40*12)/C42)*C14)*E9</f>
         <v>5582.4908594402759</v>
       </c>
       <c r="D43" s="33">
-        <f>(((O18-D40*12)/D42)*C14)*D9</f>
+        <f>(((O18-D40*12)/D42)*C14)*F9</f>
         <v>5036.3776231906841</v>
       </c>
       <c r="E43" s="33">
-        <f>($O$18/E42)*E9</f>
+        <f>($O$18/E42)*G9</f>
         <v>4098.6262846292948</v>
       </c>
       <c r="F43" s="34">
-        <f>($O$18/F42)*F9</f>
+        <f>($O$18/F42)*H9</f>
         <v>3335.8724691708017</v>
       </c>
       <c r="G43" s="27"/>
     </row>
     <row r="44" spans="2:14">
       <c r="B44" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="36" t="s">
+      <c r="G44" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="D44" s="36" t="s">
+      <c r="H44" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="36" t="s">
+      <c r="I44" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="36" t="s">
+      <c r="J44" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="G44" s="36" t="s">
+      <c r="K44" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="H44" s="36" t="s">
+      <c r="L44" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="I44" s="36" t="s">
+      <c r="M44" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="J44" s="36" t="s">
+      <c r="N44" s="36" t="s">
         <v>72</v>
-      </c>
-      <c r="K44" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="L44" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="M44" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="N44" s="36" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="45" spans="2:14">
       <c r="B45" s="35" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C45" s="37">
         <f t="shared" ref="C45:N45" si="2">$C$43*C$20</f>
@@ -12697,7 +12725,7 @@
     </row>
     <row r="46" spans="2:14">
       <c r="B46" s="35" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C46" s="37">
         <f t="shared" ref="C46:N46" si="3">$D$43*C$20</f>
@@ -12750,7 +12778,7 @@
     </row>
     <row r="47" spans="2:14">
       <c r="B47" s="35" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C47" s="37">
         <f t="shared" ref="C47:N47" si="4">$E$43*C$20</f>
@@ -12803,7 +12831,7 @@
     </row>
     <row r="48" spans="2:14">
       <c r="B48" s="36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C48" s="37">
         <f t="shared" ref="C48:N48" si="5">$F$43*C$20</f>
@@ -12856,7 +12884,7 @@
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B49" s="1" t="str">
         <f>_xlfn.LET(
@@ -12913,7 +12941,7 @@
     </row>
     <row r="50" spans="1:15">
       <c r="B50" s="38" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C50" s="39">
         <f>CHOOSE(MATCH($B$49,{"중부1","중부2","남부","제주"},0),COP_계산기!C14,COP_계산기!C18,COP_계산기!C22,COP_계산기!C26)</f>
@@ -12984,10 +13012,10 @@
     </row>
     <row r="52" spans="1:15">
       <c r="A52" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B52" s="40" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C52"/>
       <c r="D52"/>
@@ -13004,7 +13032,7 @@
     </row>
     <row r="53" spans="1:15">
       <c r="B53" s="41" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C53" s="37">
         <f t="shared" ref="C53:N53" si="6">C45/C$50</f>
@@ -13057,7 +13085,7 @@
     </row>
     <row r="54" spans="1:15">
       <c r="B54" s="41" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C54" s="37">
         <f t="shared" ref="C54:N54" si="7">C46/C$50</f>
@@ -13110,7 +13138,7 @@
     </row>
     <row r="55" spans="1:15">
       <c r="B55" s="41" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C55" s="37">
         <f t="shared" ref="C55:N55" si="8">C47/C$50</f>
@@ -13163,7 +13191,7 @@
     </row>
     <row r="56" spans="1:15">
       <c r="B56" s="36" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C56" s="37">
         <f t="shared" ref="C56:N56" si="9">C48/C$50</f>
@@ -13287,10 +13315,10 @@
     </row>
     <row r="63" spans="1:15">
       <c r="B63" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C63" s="171" t="s">
-        <v>468</v>
+        <v>82</v>
+      </c>
+      <c r="C63" s="170" t="s">
+        <v>464</v>
       </c>
       <c r="D63" s="163"/>
       <c r="E63" s="164"/>
@@ -13298,50 +13326,55 @@
       <c r="G63" s="27"/>
     </row>
     <row r="64" spans="1:15">
-      <c r="B64" s="167" t="s">
-        <v>469</v>
+      <c r="B64" s="166" t="s">
+        <v>465</v>
       </c>
       <c r="C64" s="165" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D64" s="165" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E64" s="165" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F64" s="164" t="s">
-        <v>60</v>
-      </c>
-      <c r="G64" s="167" t="s">
-        <v>465</v>
+        <v>56</v>
+      </c>
+      <c r="G64" s="166" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
         <v>2026</v>
       </c>
-      <c r="B65" s="173">
+      <c r="B65" s="172">
         <v>1</v>
       </c>
       <c r="C65" s="46">
-        <f>$C$43/1000*C10</f>
+        <f>$C$43/1000*E10</f>
         <v>1.2196528942907547</v>
       </c>
       <c r="D65" s="135">
-        <f>($D$43/1000)*D10</f>
+        <f>($D$43/1000)*F10</f>
         <v>1.219652894290755</v>
       </c>
       <c r="E65" s="134">
-        <f>(E43/1000)*E10</f>
+        <f>(E43/1000)*G10</f>
         <v>1.2556071203931318</v>
       </c>
       <c r="F65" s="134">
-        <f>(F43/1000)*F10</f>
+        <f>(F43/1000)*H10</f>
         <v>0.85250074212142846</v>
       </c>
-      <c r="G65" s="168">
-        <f>$C$43/1000*G10</f>
+      <c r="G65" s="167" cm="1">
+        <f t="array" ref="G65">_xlfn.IFS(
+TRIM(C8)="가스 콘덴싱보일러",C43/1000*I10,
+TRIM(C8)="가스 일반보일러",D43/1000*I10,
+TRIM(C8)="등유 보일러",E43/1000*I10,
+TRIM(C8)="LPG 보일러",F43/1000*I10
+)</f>
         <v>0.73258583848611414</v>
       </c>
     </row>
@@ -13349,7 +13382,7 @@
       <c r="A66">
         <v>2027</v>
       </c>
-      <c r="B66" s="174">
+      <c r="B66" s="173">
         <v>2</v>
       </c>
       <c r="C66" s="46">
@@ -13377,7 +13410,7 @@
       <c r="A67">
         <v>2028</v>
       </c>
-      <c r="B67" s="174">
+      <c r="B67" s="173">
         <v>3</v>
       </c>
       <c r="C67" s="46">
@@ -13397,7 +13430,7 @@
         <v>0.85250074212142846</v>
       </c>
       <c r="G67" s="46">
-        <f t="shared" ref="G67:G82" si="15">$G$65+(B67-1)*($G$77-$G$65)/12</f>
+        <f t="shared" ref="G67:G76" si="15">$G$65+(B67-1)*($G$77-$G$65)/12</f>
         <v>0.64942205893670524</v>
       </c>
     </row>
@@ -13405,7 +13438,7 @@
       <c r="A68">
         <v>2029</v>
       </c>
-      <c r="B68" s="174">
+      <c r="B68" s="173">
         <v>4</v>
       </c>
       <c r="C68" s="46">
@@ -13433,7 +13466,7 @@
       <c r="A69">
         <v>2030</v>
       </c>
-      <c r="B69" s="173">
+      <c r="B69" s="172">
         <v>5</v>
       </c>
       <c r="C69" s="46">
@@ -13461,7 +13494,7 @@
       <c r="A70">
         <v>2031</v>
       </c>
-      <c r="B70" s="174">
+      <c r="B70" s="173">
         <v>6</v>
       </c>
       <c r="C70" s="46">
@@ -13489,7 +13522,7 @@
       <c r="A71">
         <v>2032</v>
       </c>
-      <c r="B71" s="174">
+      <c r="B71" s="173">
         <v>7</v>
       </c>
       <c r="C71" s="46">
@@ -13517,7 +13550,7 @@
       <c r="A72">
         <v>2033</v>
       </c>
-      <c r="B72" s="174">
+      <c r="B72" s="173">
         <v>8</v>
       </c>
       <c r="C72" s="46">
@@ -13545,7 +13578,7 @@
       <c r="A73">
         <v>2034</v>
       </c>
-      <c r="B73" s="173">
+      <c r="B73" s="172">
         <v>9</v>
       </c>
       <c r="C73" s="46">
@@ -13573,7 +13606,7 @@
       <c r="A74">
         <v>2035</v>
       </c>
-      <c r="B74" s="174">
+      <c r="B74" s="173">
         <v>10</v>
       </c>
       <c r="C74" s="46">
@@ -13601,7 +13634,7 @@
       <c r="A75">
         <v>2036</v>
       </c>
-      <c r="B75" s="174">
+      <c r="B75" s="173">
         <v>11</v>
       </c>
       <c r="C75" s="46">
@@ -13629,7 +13662,7 @@
       <c r="A76">
         <v>2037</v>
       </c>
-      <c r="B76" s="174">
+      <c r="B76" s="173">
         <v>12</v>
       </c>
       <c r="C76" s="46">
@@ -13657,7 +13690,7 @@
       <c r="A77">
         <v>2038</v>
       </c>
-      <c r="B77" s="173">
+      <c r="B77" s="172">
         <v>13</v>
       </c>
       <c r="C77" s="46">
@@ -13676,17 +13709,22 @@
         <f t="shared" si="14"/>
         <v>0.85250074212142846</v>
       </c>
-      <c r="G77" s="168">
-        <f>$C$43/1000*H10</f>
+      <c r="G77" s="167" cm="1">
+        <f t="array" ref="G77">_xlfn.IFS(
+TRIM(C8)="가스 콘덴싱보일러",C43/1000*J10,
+TRIM(C8)="가스 일반보일러",D43/1000*J10,
+TRIM(C8)="등유 보일러",E43/1000*J10,
+TRIM(C8)="LPG 보일러",F43/1000*J10
+)</f>
         <v>0.2336031611896604</v>
       </c>
-      <c r="H77" s="169"/>
+      <c r="H77" s="168"/>
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
         <v>2039</v>
       </c>
-      <c r="B78" s="174">
+      <c r="B78" s="173">
         <v>14</v>
       </c>
       <c r="C78" s="46">
@@ -13706,15 +13744,15 @@
         <v>0.85250074212142846</v>
       </c>
       <c r="G78" s="46">
-        <f t="shared" si="15"/>
-        <v>0.19202127141495595</v>
+        <f>G77-$G$77/12</f>
+        <v>0.21413623109052204</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
         <v>2040</v>
       </c>
-      <c r="B79" s="174">
+      <c r="B79" s="173">
         <v>15</v>
       </c>
       <c r="C79" s="46">
@@ -13734,15 +13772,15 @@
         <v>0.85250074212142846</v>
       </c>
       <c r="G79" s="46">
-        <f t="shared" si="15"/>
-        <v>0.1504393816402515</v>
+        <f t="shared" ref="G79:G82" si="16">G78-$G$77/12</f>
+        <v>0.19466930099138369</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
         <v>2041</v>
       </c>
-      <c r="B80" s="173">
+      <c r="B80" s="172">
         <v>16</v>
       </c>
       <c r="C80" s="46">
@@ -13762,15 +13800,15 @@
         <v>0.85250074212142846</v>
       </c>
       <c r="G80" s="46">
-        <f t="shared" si="15"/>
-        <v>0.10885749186554694</v>
+        <f t="shared" si="16"/>
+        <v>0.17520237089224533</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
         <v>2042</v>
       </c>
-      <c r="B81" s="174">
+      <c r="B81" s="173">
         <v>17</v>
       </c>
       <c r="C81" s="46">
@@ -13790,15 +13828,15 @@
         <v>0.85250074212142846</v>
       </c>
       <c r="G81" s="46">
-        <f t="shared" si="15"/>
-        <v>6.727560209084249E-2</v>
+        <f t="shared" si="16"/>
+        <v>0.15573544079310697</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
         <v>2043</v>
       </c>
-      <c r="B82" s="174">
+      <c r="B82" s="173">
         <v>18</v>
       </c>
       <c r="C82" s="46">
@@ -13818,55 +13856,55 @@
         <v>0.85250074212142846</v>
       </c>
       <c r="G82" s="46">
-        <f t="shared" si="15"/>
-        <v>2.569371231613804E-2</v>
+        <f t="shared" si="16"/>
+        <v>0.13626851069396861</v>
       </c>
     </row>
     <row r="83" spans="1:7">
-      <c r="B83" s="172" t="s">
-        <v>467</v>
-      </c>
-      <c r="C83" s="170">
+      <c r="B83" s="171" t="s">
+        <v>463</v>
+      </c>
+      <c r="C83" s="169">
         <f>SUM(C65:C82)</f>
         <v>21.953752097233583</v>
       </c>
-      <c r="D83" s="170">
-        <f t="shared" ref="D83:G83" si="16">SUM(D65:D82)</f>
+      <c r="D83" s="169">
+        <f t="shared" ref="D83:G83" si="17">SUM(D65:D82)</f>
         <v>21.953752097233583</v>
       </c>
-      <c r="E83" s="170">
-        <f t="shared" si="16"/>
+      <c r="E83" s="169">
+        <f t="shared" si="17"/>
         <v>22.600928167076376</v>
       </c>
-      <c r="F83" s="170">
-        <f t="shared" si="16"/>
+      <c r="F83" s="169">
+        <f t="shared" si="17"/>
         <v>15.345013358185712</v>
       </c>
-      <c r="G83" s="170">
-        <f t="shared" si="16"/>
-        <v>6.8245159572202683</v>
+      <c r="G83" s="169">
+        <f t="shared" si="17"/>
+        <v>7.1562403523537599</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="B86" s="47" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C86" s="48" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D86" s="48" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E86" s="49" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="B87" s="50" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D87" s="28">
         <v>1</v>
@@ -13878,10 +13916,10 @@
     </row>
     <row r="88" spans="1:7">
       <c r="B88" s="50" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D88" s="52">
         <v>36.6</v>
@@ -13892,10 +13930,10 @@
     </row>
     <row r="89" spans="1:7">
       <c r="B89" s="54" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C89" s="55" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D89" s="56">
         <v>50.2</v>
@@ -13906,6 +13944,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="52" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8" xr:uid="{958DBC3A-1CEA-43DD-A80B-8E8D48A05006}">
+      <formula1>E8:H8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13" xr:uid="{01773ED9-6C02-4385-ACDB-BA2D6E922BB4}">
+      <formula1>$E$13:$G$13</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing r:id="rId1"/>
@@ -13941,54 +13987,54 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>29</v>
-      </c>
-      <c r="K1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C2" s="58">
         <v>0.205290240813082</v>
@@ -14029,10 +14075,10 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C3" s="59">
         <v>0.19641921152213601</v>
@@ -14073,10 +14119,10 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C4" s="59">
         <v>0.202965578813149</v>
@@ -14117,10 +14163,10 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C5" s="59">
         <v>0.2271183528531</v>
@@ -14161,10 +14207,10 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C6" s="59">
         <v>0.20927893408395001</v>
@@ -14205,10 +14251,10 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C7" s="59">
         <v>0.24781327365563499</v>
@@ -14249,10 +14295,10 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C8" s="59">
         <v>0.20506540950215699</v>
@@ -14293,10 +14339,10 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C9" s="59">
         <v>0.20974002744717599</v>
@@ -14337,10 +14383,10 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C10" s="59">
         <v>0.18966287139541299</v>
@@ -14381,10 +14427,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C11" s="59">
         <v>0.202652811113675</v>
@@ -14425,10 +14471,10 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C12" s="59">
         <v>0.20253037914500499</v>
@@ -14469,10 +14515,10 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C13" s="59">
         <v>0.20021253334828401</v>
@@ -14513,10 +14559,10 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C14" s="59">
         <v>0.20197157222700399</v>
@@ -14557,10 +14603,10 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C15" s="59">
         <v>0.18512214934004201</v>
@@ -14601,10 +14647,10 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C16" s="59">
         <v>0.25461522802861197</v>
@@ -14645,10 +14691,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C17" s="59">
         <v>0.20700978630783101</v>
@@ -14689,10 +14735,10 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C18" s="59">
         <v>0.19463922550399301</v>
@@ -14733,10 +14779,10 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C19" s="59">
         <v>0.17281165713725</v>
@@ -14790,18 +14836,18 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D2" t="str">
         <f t="array" ref="D2:D18">_xlfn._xlws.SORT(_xlfn.UNIQUE(A2:A229))</f>
@@ -14814,10 +14860,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D3" t="str">
         <v>경기도</v>
@@ -14828,10 +14874,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D4" t="str">
         <v>경상남도</v>
@@ -14842,10 +14888,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" t="str">
         <v>경상북도</v>
@@ -14856,10 +14902,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D6" t="str">
         <v>광주광역시</v>
@@ -14870,10 +14916,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D7" t="str">
         <v>대구광역시</v>
@@ -14884,10 +14930,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D8" t="str">
         <v>대전광역시</v>
@@ -14898,10 +14944,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D9" t="str">
         <v>부산광역시</v>
@@ -14912,10 +14958,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D10" t="str">
         <v>서울특별시</v>
@@ -14926,10 +14972,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D11" t="str">
         <v>세종특별자치시</v>
@@ -14940,10 +14986,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D12" t="str">
         <v>울산광역시</v>
@@ -14954,10 +15000,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D13" t="str">
         <v>인천광역시</v>
@@ -14968,10 +15014,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D14" t="str">
         <v>전라남도</v>
@@ -14982,10 +15028,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D15" t="str">
         <v>전라북도</v>
@@ -14996,10 +15042,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D16" t="str">
         <v>제주특별자치도</v>
@@ -15010,10 +15056,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D17" t="str">
         <v>충청남도</v>
@@ -15024,10 +15070,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D18" t="str">
         <v>충청북도</v>
@@ -15038,10 +15084,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E19" t="str">
         <v>합천군</v>
@@ -15049,1682 +15095,1682 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B157" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -16746,100 +16792,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="25.5" customHeight="1">
-      <c r="A1" s="175" t="s">
-        <v>339</v>
-      </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
-      <c r="M1" s="175"/>
-      <c r="N1" s="175"/>
-      <c r="O1" s="175"/>
-      <c r="P1" s="175"/>
-      <c r="Q1" s="175"/>
-      <c r="R1" s="175"/>
-      <c r="S1" s="175"/>
-      <c r="T1" s="175"/>
-      <c r="U1" s="175"/>
-      <c r="V1" s="175"/>
-      <c r="W1" s="175"/>
-      <c r="X1" s="175"/>
-      <c r="Y1" s="175"/>
-      <c r="Z1" s="175"/>
+      <c r="A1" s="174" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="174"/>
+      <c r="L1" s="174"/>
+      <c r="M1" s="174"/>
+      <c r="N1" s="174"/>
+      <c r="O1" s="174"/>
+      <c r="P1" s="174"/>
+      <c r="Q1" s="174"/>
+      <c r="R1" s="174"/>
+      <c r="S1" s="174"/>
+      <c r="T1" s="174"/>
+      <c r="U1" s="174"/>
+      <c r="V1" s="174"/>
+      <c r="W1" s="174"/>
+      <c r="X1" s="174"/>
+      <c r="Y1" s="174"/>
+      <c r="Z1" s="174"/>
     </row>
     <row r="3" spans="1:26" ht="21.75" customHeight="1">
-      <c r="A3" s="176" t="s">
-        <v>340</v>
-      </c>
-      <c r="B3" s="176"/>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="176"/>
-      <c r="I3" s="176"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="176"/>
-      <c r="L3" s="176"/>
-      <c r="M3" s="176"/>
-      <c r="N3" s="176"/>
+      <c r="A3" s="175" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="175"/>
+      <c r="K3" s="175"/>
+      <c r="L3" s="175"/>
+      <c r="M3" s="175"/>
+      <c r="N3" s="175"/>
     </row>
     <row r="4" spans="1:26" ht="21.75" customHeight="1">
       <c r="A4" s="61" t="s">
+        <v>337</v>
+      </c>
+      <c r="B4" s="62" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>340</v>
+      </c>
+      <c r="E4" s="62" t="s">
         <v>341</v>
       </c>
-      <c r="B4" s="62" t="s">
+      <c r="F4" s="62" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="G4" s="62" t="s">
         <v>343</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="H4" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="E4" s="62" t="s">
+      <c r="I4" s="62" t="s">
         <v>345</v>
       </c>
-      <c r="F4" s="62" t="s">
+      <c r="J4" s="62" t="s">
         <v>346</v>
       </c>
-      <c r="G4" s="62" t="s">
+      <c r="K4" s="62" t="s">
         <v>347</v>
       </c>
-      <c r="H4" s="62" t="s">
+      <c r="L4" s="62" t="s">
         <v>348</v>
       </c>
-      <c r="I4" s="62" t="s">
+      <c r="M4" s="62" t="s">
         <v>349</v>
       </c>
-      <c r="J4" s="62" t="s">
+      <c r="N4" s="61" t="s">
         <v>350</v>
-      </c>
-      <c r="K4" s="62" t="s">
-        <v>351</v>
-      </c>
-      <c r="L4" s="62" t="s">
-        <v>352</v>
-      </c>
-      <c r="M4" s="62" t="s">
-        <v>353</v>
-      </c>
-      <c r="N4" s="61" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="19.5" customHeight="1">
       <c r="A5" s="63" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B5" s="64">
         <v>-9.1999999999999993</v>
@@ -16884,7 +16930,7 @@
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="63" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B6" s="64">
         <v>9.8000000000000007</v>
@@ -18239,70 +18285,70 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A30" s="177" t="s">
-        <v>357</v>
-      </c>
-      <c r="B30" s="177"/>
-      <c r="C30" s="177"/>
-      <c r="D30" s="177"/>
-      <c r="E30" s="177"/>
-      <c r="F30" s="177"/>
-      <c r="G30" s="177"/>
-      <c r="H30" s="177"/>
-      <c r="I30" s="177"/>
-      <c r="J30" s="177"/>
-      <c r="K30" s="177"/>
-      <c r="L30" s="177"/>
-      <c r="M30" s="177"/>
-      <c r="N30" s="177"/>
+      <c r="A30" s="176" t="s">
+        <v>353</v>
+      </c>
+      <c r="B30" s="176"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="176"/>
+      <c r="E30" s="176"/>
+      <c r="F30" s="176"/>
+      <c r="G30" s="176"/>
+      <c r="H30" s="176"/>
+      <c r="I30" s="176"/>
+      <c r="J30" s="176"/>
+      <c r="K30" s="176"/>
+      <c r="L30" s="176"/>
+      <c r="M30" s="176"/>
+      <c r="N30" s="176"/>
     </row>
     <row r="31" spans="1:14" ht="21.75" customHeight="1">
       <c r="A31" s="68" t="s">
+        <v>337</v>
+      </c>
+      <c r="B31" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="C31" s="69" t="s">
+        <v>339</v>
+      </c>
+      <c r="D31" s="69" t="s">
+        <v>340</v>
+      </c>
+      <c r="E31" s="69" t="s">
         <v>341</v>
       </c>
-      <c r="B31" s="69" t="s">
+      <c r="F31" s="69" t="s">
         <v>342</v>
       </c>
-      <c r="C31" s="69" t="s">
+      <c r="G31" s="69" t="s">
         <v>343</v>
       </c>
-      <c r="D31" s="69" t="s">
+      <c r="H31" s="69" t="s">
         <v>344</v>
       </c>
-      <c r="E31" s="69" t="s">
+      <c r="I31" s="69" t="s">
         <v>345</v>
       </c>
-      <c r="F31" s="69" t="s">
+      <c r="J31" s="69" t="s">
         <v>346</v>
       </c>
-      <c r="G31" s="69" t="s">
+      <c r="K31" s="69" t="s">
         <v>347</v>
       </c>
-      <c r="H31" s="69" t="s">
+      <c r="L31" s="69" t="s">
         <v>348</v>
       </c>
-      <c r="I31" s="69" t="s">
+      <c r="M31" s="69" t="s">
         <v>349</v>
       </c>
-      <c r="J31" s="69" t="s">
+      <c r="N31" s="68" t="s">
         <v>350</v>
-      </c>
-      <c r="K31" s="69" t="s">
-        <v>351</v>
-      </c>
-      <c r="L31" s="69" t="s">
-        <v>352</v>
-      </c>
-      <c r="M31" s="69" t="s">
-        <v>353</v>
-      </c>
-      <c r="N31" s="68" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="19.5" customHeight="1">
       <c r="A32" s="70" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B32" s="71">
         <v>-1.8</v>
@@ -18347,7 +18393,7 @@
     </row>
     <row r="33" spans="1:14" ht="18" customHeight="1">
       <c r="A33" s="70" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B33" s="71">
         <v>7.2</v>
@@ -19702,70 +19748,70 @@
       </c>
     </row>
     <row r="57" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A57" s="178" t="s">
-        <v>358</v>
-      </c>
-      <c r="B57" s="178"/>
-      <c r="C57" s="178"/>
-      <c r="D57" s="178"/>
-      <c r="E57" s="178"/>
-      <c r="F57" s="178"/>
-      <c r="G57" s="178"/>
-      <c r="H57" s="178"/>
-      <c r="I57" s="178"/>
-      <c r="J57" s="178"/>
-      <c r="K57" s="178"/>
-      <c r="L57" s="178"/>
-      <c r="M57" s="178"/>
-      <c r="N57" s="178"/>
+      <c r="A57" s="177" t="s">
+        <v>354</v>
+      </c>
+      <c r="B57" s="177"/>
+      <c r="C57" s="177"/>
+      <c r="D57" s="177"/>
+      <c r="E57" s="177"/>
+      <c r="F57" s="177"/>
+      <c r="G57" s="177"/>
+      <c r="H57" s="177"/>
+      <c r="I57" s="177"/>
+      <c r="J57" s="177"/>
+      <c r="K57" s="177"/>
+      <c r="L57" s="177"/>
+      <c r="M57" s="177"/>
+      <c r="N57" s="177"/>
     </row>
     <row r="58" spans="1:14" ht="21.75" customHeight="1">
       <c r="A58" s="73" t="s">
+        <v>337</v>
+      </c>
+      <c r="B58" s="74" t="s">
+        <v>338</v>
+      </c>
+      <c r="C58" s="74" t="s">
+        <v>339</v>
+      </c>
+      <c r="D58" s="74" t="s">
+        <v>340</v>
+      </c>
+      <c r="E58" s="74" t="s">
         <v>341</v>
       </c>
-      <c r="B58" s="74" t="s">
+      <c r="F58" s="74" t="s">
         <v>342</v>
       </c>
-      <c r="C58" s="74" t="s">
+      <c r="G58" s="74" t="s">
         <v>343</v>
       </c>
-      <c r="D58" s="74" t="s">
+      <c r="H58" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="E58" s="74" t="s">
+      <c r="I58" s="74" t="s">
         <v>345</v>
       </c>
-      <c r="F58" s="74" t="s">
+      <c r="J58" s="74" t="s">
         <v>346</v>
       </c>
-      <c r="G58" s="74" t="s">
+      <c r="K58" s="74" t="s">
         <v>347</v>
       </c>
-      <c r="H58" s="74" t="s">
+      <c r="L58" s="74" t="s">
         <v>348</v>
       </c>
-      <c r="I58" s="74" t="s">
+      <c r="M58" s="74" t="s">
         <v>349</v>
       </c>
-      <c r="J58" s="74" t="s">
+      <c r="N58" s="73" t="s">
         <v>350</v>
-      </c>
-      <c r="K58" s="74" t="s">
-        <v>351</v>
-      </c>
-      <c r="L58" s="74" t="s">
-        <v>352</v>
-      </c>
-      <c r="M58" s="74" t="s">
-        <v>353</v>
-      </c>
-      <c r="N58" s="73" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="19.5" customHeight="1">
       <c r="A59" s="75" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B59" s="76">
         <v>3.8</v>
@@ -19810,7 +19856,7 @@
     </row>
     <row r="60" spans="1:14" ht="18" customHeight="1">
       <c r="A60" s="75" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B60" s="76">
         <v>6.2</v>
@@ -21165,70 +21211,70 @@
       </c>
     </row>
     <row r="84" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A84" s="179" t="s">
-        <v>359</v>
-      </c>
-      <c r="B84" s="179"/>
-      <c r="C84" s="179"/>
-      <c r="D84" s="179"/>
-      <c r="E84" s="179"/>
-      <c r="F84" s="179"/>
-      <c r="G84" s="179"/>
-      <c r="H84" s="179"/>
-      <c r="I84" s="179"/>
-      <c r="J84" s="179"/>
-      <c r="K84" s="179"/>
-      <c r="L84" s="179"/>
-      <c r="M84" s="179"/>
-      <c r="N84" s="179"/>
+      <c r="A84" s="178" t="s">
+        <v>355</v>
+      </c>
+      <c r="B84" s="178"/>
+      <c r="C84" s="178"/>
+      <c r="D84" s="178"/>
+      <c r="E84" s="178"/>
+      <c r="F84" s="178"/>
+      <c r="G84" s="178"/>
+      <c r="H84" s="178"/>
+      <c r="I84" s="178"/>
+      <c r="J84" s="178"/>
+      <c r="K84" s="178"/>
+      <c r="L84" s="178"/>
+      <c r="M84" s="178"/>
+      <c r="N84" s="178"/>
     </row>
     <row r="85" spans="1:14" ht="21.75" customHeight="1">
       <c r="A85" s="78" t="s">
+        <v>337</v>
+      </c>
+      <c r="B85" s="79" t="s">
+        <v>338</v>
+      </c>
+      <c r="C85" s="79" t="s">
+        <v>339</v>
+      </c>
+      <c r="D85" s="79" t="s">
+        <v>340</v>
+      </c>
+      <c r="E85" s="79" t="s">
         <v>341</v>
       </c>
-      <c r="B85" s="79" t="s">
+      <c r="F85" s="79" t="s">
         <v>342</v>
       </c>
-      <c r="C85" s="79" t="s">
+      <c r="G85" s="79" t="s">
         <v>343</v>
       </c>
-      <c r="D85" s="79" t="s">
+      <c r="H85" s="79" t="s">
         <v>344</v>
       </c>
-      <c r="E85" s="79" t="s">
+      <c r="I85" s="79" t="s">
         <v>345</v>
       </c>
-      <c r="F85" s="79" t="s">
+      <c r="J85" s="79" t="s">
         <v>346</v>
       </c>
-      <c r="G85" s="79" t="s">
+      <c r="K85" s="79" t="s">
         <v>347</v>
       </c>
-      <c r="H85" s="79" t="s">
+      <c r="L85" s="79" t="s">
         <v>348</v>
       </c>
-      <c r="I85" s="79" t="s">
+      <c r="M85" s="79" t="s">
         <v>349</v>
       </c>
-      <c r="J85" s="79" t="s">
+      <c r="N85" s="78" t="s">
         <v>350</v>
-      </c>
-      <c r="K85" s="79" t="s">
-        <v>351</v>
-      </c>
-      <c r="L85" s="79" t="s">
-        <v>352</v>
-      </c>
-      <c r="M85" s="79" t="s">
-        <v>353</v>
-      </c>
-      <c r="N85" s="78" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="19.5" customHeight="1">
       <c r="A86" s="80" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B86" s="81">
         <v>6.2</v>
@@ -21273,7 +21319,7 @@
     </row>
     <row r="87" spans="1:14" ht="18" customHeight="1">
       <c r="A87" s="80" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B87" s="81">
         <v>5.8</v>
@@ -22715,98 +22761,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.75" customHeight="1">
-      <c r="A1" s="180" t="s">
-        <v>360</v>
-      </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="180"/>
-      <c r="F1" s="180"/>
-      <c r="G1" s="180"/>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
-      <c r="J1" s="180"/>
-      <c r="K1" s="180"/>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
-      <c r="N1" s="180"/>
-      <c r="O1" s="180"/>
-      <c r="P1" s="180"/>
-      <c r="Q1" s="180"/>
-      <c r="R1" s="180"/>
+      <c r="A1" s="185" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
+      <c r="K1" s="185"/>
+      <c r="L1" s="185"/>
+      <c r="M1" s="185"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="185"/>
+      <c r="P1" s="185"/>
+      <c r="Q1" s="185"/>
+      <c r="R1" s="185"/>
     </row>
     <row r="3" spans="1:18" ht="21.75" customHeight="1">
-      <c r="A3" s="176" t="s">
-        <v>361</v>
-      </c>
-      <c r="B3" s="176"/>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
+      <c r="A3" s="175" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
     </row>
     <row r="4" spans="1:18" ht="21.75" customHeight="1">
-      <c r="A4" s="181" t="s">
-        <v>362</v>
-      </c>
-      <c r="B4" s="181"/>
-      <c r="C4" s="181"/>
+      <c r="A4" s="182" t="s">
+        <v>358</v>
+      </c>
+      <c r="B4" s="182"/>
+      <c r="C4" s="182"/>
       <c r="D4" s="83">
         <v>55</v>
       </c>
-      <c r="E4" s="182" t="s">
-        <v>363</v>
-      </c>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="182"/>
-      <c r="I4" s="182"/>
-      <c r="J4" s="182"/>
-      <c r="K4" s="182"/>
-      <c r="L4" s="182"/>
-      <c r="M4" s="182"/>
-      <c r="N4" s="182"/>
-      <c r="O4" s="182"/>
-      <c r="P4" s="182"/>
-      <c r="Q4" s="182"/>
-      <c r="R4" s="182"/>
+      <c r="E4" s="184" t="s">
+        <v>359</v>
+      </c>
+      <c r="F4" s="184"/>
+      <c r="G4" s="184"/>
+      <c r="H4" s="184"/>
+      <c r="I4" s="184"/>
+      <c r="J4" s="184"/>
+      <c r="K4" s="184"/>
+      <c r="L4" s="184"/>
+      <c r="M4" s="184"/>
+      <c r="N4" s="184"/>
+      <c r="O4" s="184"/>
+      <c r="P4" s="184"/>
+      <c r="Q4" s="184"/>
+      <c r="R4" s="184"/>
     </row>
     <row r="5" spans="1:18" ht="21.75" customHeight="1">
-      <c r="A5" s="181" t="s">
-        <v>364</v>
-      </c>
-      <c r="B5" s="181"/>
-      <c r="C5" s="181"/>
+      <c r="A5" s="182" t="s">
+        <v>360</v>
+      </c>
+      <c r="B5" s="182"/>
+      <c r="C5" s="182"/>
       <c r="D5" s="84">
         <v>0.5</v>
       </c>
-      <c r="E5" s="182" t="s">
-        <v>365</v>
-      </c>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="182"/>
-      <c r="J5" s="182"/>
-      <c r="K5" s="182"/>
-      <c r="L5" s="182"/>
-      <c r="M5" s="182"/>
-      <c r="N5" s="182"/>
-      <c r="O5" s="182"/>
-      <c r="P5" s="182"/>
-      <c r="Q5" s="182"/>
-      <c r="R5" s="182"/>
+      <c r="E5" s="184" t="s">
+        <v>361</v>
+      </c>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="184"/>
+      <c r="L5" s="184"/>
+      <c r="M5" s="184"/>
+      <c r="N5" s="184"/>
+      <c r="O5" s="184"/>
+      <c r="P5" s="184"/>
+      <c r="Q5" s="184"/>
+      <c r="R5" s="184"/>
     </row>
     <row r="6" spans="1:18" ht="21.75" customHeight="1">
-      <c r="A6" s="181" t="s">
-        <v>366</v>
-      </c>
-      <c r="B6" s="181"/>
-      <c r="C6" s="181"/>
+      <c r="A6" s="182" t="s">
+        <v>362</v>
+      </c>
+      <c r="B6" s="182"/>
+      <c r="C6" s="182"/>
       <c r="D6" s="83">
         <v>18</v>
       </c>
       <c r="E6" s="183" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F6" s="183"/>
       <c r="G6" s="183"/>
@@ -22823,115 +22869,115 @@
       <c r="R6" s="183"/>
     </row>
     <row r="7" spans="1:18" ht="21.75" customHeight="1">
-      <c r="A7" s="181" t="s">
-        <v>368</v>
-      </c>
-      <c r="B7" s="181"/>
-      <c r="C7" s="181"/>
+      <c r="A7" s="182" t="s">
+        <v>364</v>
+      </c>
+      <c r="B7" s="182"/>
+      <c r="C7" s="182"/>
       <c r="D7" s="85">
         <v>3</v>
       </c>
-      <c r="E7" s="182" t="s">
-        <v>369</v>
-      </c>
-      <c r="F7" s="182"/>
-      <c r="G7" s="182"/>
-      <c r="H7" s="182"/>
-      <c r="I7" s="182"/>
-      <c r="J7" s="182"/>
-      <c r="K7" s="182"/>
-      <c r="L7" s="182"/>
-      <c r="M7" s="182"/>
-      <c r="N7" s="182"/>
-      <c r="O7" s="182"/>
-      <c r="P7" s="182"/>
-      <c r="Q7" s="182"/>
-      <c r="R7" s="182"/>
+      <c r="E7" s="184" t="s">
+        <v>365</v>
+      </c>
+      <c r="F7" s="184"/>
+      <c r="G7" s="184"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="184"/>
+      <c r="J7" s="184"/>
+      <c r="K7" s="184"/>
+      <c r="L7" s="184"/>
+      <c r="M7" s="184"/>
+      <c r="N7" s="184"/>
+      <c r="O7" s="184"/>
+      <c r="P7" s="184"/>
+      <c r="Q7" s="184"/>
+      <c r="R7" s="184"/>
     </row>
     <row r="9" spans="1:18" ht="18" customHeight="1">
-      <c r="A9" s="182" t="s">
-        <v>370</v>
-      </c>
-      <c r="B9" s="182"/>
-      <c r="C9" s="182"/>
-      <c r="D9" s="182"/>
-      <c r="E9" s="182"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="182"/>
-      <c r="H9" s="182"/>
-      <c r="I9" s="182"/>
-      <c r="J9" s="182"/>
-      <c r="K9" s="182"/>
-      <c r="L9" s="182"/>
-      <c r="M9" s="182"/>
-      <c r="N9" s="182"/>
-      <c r="O9" s="182"/>
-      <c r="P9" s="182"/>
-      <c r="Q9" s="182"/>
-      <c r="R9" s="182"/>
+      <c r="A9" s="184" t="s">
+        <v>366</v>
+      </c>
+      <c r="B9" s="184"/>
+      <c r="C9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
+      <c r="J9" s="184"/>
+      <c r="K9" s="184"/>
+      <c r="L9" s="184"/>
+      <c r="M9" s="184"/>
+      <c r="N9" s="184"/>
+      <c r="O9" s="184"/>
+      <c r="P9" s="184"/>
+      <c r="Q9" s="184"/>
+      <c r="R9" s="184"/>
     </row>
     <row r="11" spans="1:18" ht="24" customHeight="1">
       <c r="A11" s="86" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B11" s="86" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="D11" s="87" t="s">
+        <v>339</v>
+      </c>
+      <c r="E11" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="F11" s="87" t="s">
+        <v>341</v>
+      </c>
+      <c r="G11" s="87" t="s">
+        <v>342</v>
+      </c>
+      <c r="H11" s="87" t="s">
+        <v>343</v>
+      </c>
+      <c r="I11" s="87" t="s">
+        <v>344</v>
+      </c>
+      <c r="J11" s="87" t="s">
+        <v>345</v>
+      </c>
+      <c r="K11" s="87" t="s">
+        <v>346</v>
+      </c>
+      <c r="L11" s="87" t="s">
+        <v>347</v>
+      </c>
+      <c r="M11" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="N11" s="87" t="s">
+        <v>349</v>
+      </c>
+      <c r="O11" s="86" t="s">
+        <v>368</v>
+      </c>
+      <c r="P11" s="88" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q11" s="89" t="s">
+        <v>370</v>
+      </c>
+      <c r="R11" s="89" t="s">
         <v>371</v>
-      </c>
-      <c r="C11" s="87" t="s">
-        <v>342</v>
-      </c>
-      <c r="D11" s="87" t="s">
-        <v>343</v>
-      </c>
-      <c r="E11" s="87" t="s">
-        <v>344</v>
-      </c>
-      <c r="F11" s="87" t="s">
-        <v>345</v>
-      </c>
-      <c r="G11" s="87" t="s">
-        <v>346</v>
-      </c>
-      <c r="H11" s="87" t="s">
-        <v>347</v>
-      </c>
-      <c r="I11" s="87" t="s">
-        <v>348</v>
-      </c>
-      <c r="J11" s="87" t="s">
-        <v>349</v>
-      </c>
-      <c r="K11" s="87" t="s">
-        <v>350</v>
-      </c>
-      <c r="L11" s="87" t="s">
-        <v>351</v>
-      </c>
-      <c r="M11" s="87" t="s">
-        <v>352</v>
-      </c>
-      <c r="N11" s="87" t="s">
-        <v>353</v>
-      </c>
-      <c r="O11" s="86" t="s">
-        <v>372</v>
-      </c>
-      <c r="P11" s="88" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q11" s="89" t="s">
-        <v>374</v>
-      </c>
-      <c r="R11" s="89" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="19.5" customHeight="1">
       <c r="A12" s="90" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B12" s="91" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C12" s="64">
         <f>외기온도_시간분포!B5</f>
@@ -22985,15 +23031,15 @@
         <f>AVERAGE(C12:N12)</f>
         <v>8.2083333333333339</v>
       </c>
-      <c r="P12" s="184">
+      <c r="P12" s="179">
         <f>IFERROR(SUMPRODUCT(C13:N13,C14:N14)/SUM(C13:N13),0)</f>
         <v>2.8965836910861085</v>
       </c>
-      <c r="Q12" s="185">
+      <c r="Q12" s="180">
         <f>$D$7</f>
         <v>3</v>
       </c>
-      <c r="R12" s="186" t="str">
+      <c r="R12" s="181" t="str">
         <f>IF(P12&gt;=$D$7,"✓ 달성","✗ 미달")</f>
         <v>✗ 미달</v>
       </c>
@@ -23001,7 +23047,7 @@
     <row r="13" spans="1:18" ht="19.5" customHeight="1">
       <c r="A13" s="92"/>
       <c r="B13" s="93" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C13" s="94">
         <f>MAX(0,$D$6-C12)*31</f>
@@ -23055,14 +23101,14 @@
         <f>SUM(C13:N13)</f>
         <v>3977.2999999999997</v>
       </c>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="185"/>
-      <c r="R13" s="185"/>
+      <c r="P13" s="179"/>
+      <c r="Q13" s="180"/>
+      <c r="R13" s="180"/>
     </row>
     <row r="14" spans="1:18" ht="21.75" customHeight="1">
       <c r="A14" s="92"/>
       <c r="B14" s="93" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C14" s="96">
         <f t="shared" ref="C14:N14" si="0">$D$5*($D$4+273)/MAX(1,$D$4-C12)</f>
@@ -23116,17 +23162,17 @@
         <f>AVERAGE(C14:N14)</f>
         <v>3.7404719651563734</v>
       </c>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="185"/>
-      <c r="R14" s="185"/>
+      <c r="P14" s="179"/>
+      <c r="Q14" s="180"/>
+      <c r="R14" s="180"/>
     </row>
     <row r="15" spans="1:18" ht="6" customHeight="1"/>
     <row r="16" spans="1:18" ht="19.5" customHeight="1">
       <c r="A16" s="98" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B16" s="99" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C16" s="71">
         <f>외기온도_시간분포!B32</f>
@@ -23180,15 +23226,15 @@
         <f>AVERAGE(C16:N16)</f>
         <v>13.241666666666665</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="179">
         <f>IFERROR(SUMPRODUCT(C17:N17,C18:N18)/SUM(C17:N17),0)</f>
         <v>3.1799323891634077</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="180">
         <f>$D$7</f>
         <v>3</v>
       </c>
-      <c r="R16" s="186" t="str">
+      <c r="R16" s="181" t="str">
         <f>IF(P16&gt;=$D$7,"✓ 달성","✗ 미달")</f>
         <v>✓ 달성</v>
       </c>
@@ -23196,7 +23242,7 @@
     <row r="17" spans="1:18" ht="19.5" customHeight="1">
       <c r="A17" s="100"/>
       <c r="B17" s="101" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C17" s="102">
         <f>MAX(0,$D$6-C16)*31</f>
@@ -23250,14 +23296,14 @@
         <f>SUM(C17:N17)</f>
         <v>2540.1999999999998</v>
       </c>
-      <c r="P17" s="184"/>
-      <c r="Q17" s="185"/>
-      <c r="R17" s="185"/>
+      <c r="P17" s="179"/>
+      <c r="Q17" s="180"/>
+      <c r="R17" s="180"/>
     </row>
     <row r="18" spans="1:18" ht="21.75" customHeight="1">
       <c r="A18" s="100"/>
       <c r="B18" s="101" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C18" s="104">
         <f t="shared" ref="C18:N18" si="1">$D$5*($D$4+273)/MAX(1,$D$4-C16)</f>
@@ -23311,17 +23357,17 @@
         <f>AVERAGE(C18:N18)</f>
         <v>4.1667250810475496</v>
       </c>
-      <c r="P18" s="184"/>
-      <c r="Q18" s="185"/>
-      <c r="R18" s="185"/>
+      <c r="P18" s="179"/>
+      <c r="Q18" s="180"/>
+      <c r="R18" s="180"/>
     </row>
     <row r="19" spans="1:18" ht="6" customHeight="1"/>
     <row r="20" spans="1:18" ht="19.5" customHeight="1">
       <c r="A20" s="106" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B20" s="107" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C20" s="76">
         <f>외기온도_시간분포!B59</f>
@@ -23375,15 +23421,15 @@
         <f>AVERAGE(C20:N20)</f>
         <v>15.541666666666664</v>
       </c>
-      <c r="P20" s="184">
+      <c r="P20" s="179">
         <f>IFERROR(SUMPRODUCT(C21:N21,C22:N22)/SUM(C21:N21),0)</f>
         <v>3.4265415256081484</v>
       </c>
-      <c r="Q20" s="185">
+      <c r="Q20" s="180">
         <f>$D$7</f>
         <v>3</v>
       </c>
-      <c r="R20" s="186" t="str">
+      <c r="R20" s="181" t="str">
         <f>IF(P20&gt;=$D$7,"✓ 달성","✗ 미달")</f>
         <v>✓ 달성</v>
       </c>
@@ -23391,7 +23437,7 @@
     <row r="21" spans="1:18" ht="19.5" customHeight="1">
       <c r="A21" s="108"/>
       <c r="B21" s="109" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C21" s="110">
         <f>MAX(0,$D$6-C20)*31</f>
@@ -23445,14 +23491,14 @@
         <f>SUM(C21:N21)</f>
         <v>1747.5</v>
       </c>
-      <c r="P21" s="184"/>
-      <c r="Q21" s="185"/>
-      <c r="R21" s="185"/>
+      <c r="P21" s="179"/>
+      <c r="Q21" s="180"/>
+      <c r="R21" s="180"/>
     </row>
     <row r="22" spans="1:18" ht="21.75" customHeight="1">
       <c r="A22" s="108"/>
       <c r="B22" s="109" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C22" s="112">
         <f t="shared" ref="C22:N22" si="2">$D$5*($D$4+273)/MAX(1,$D$4-C20)</f>
@@ -23506,17 +23552,17 @@
         <f>AVERAGE(C22:N22)</f>
         <v>4.3369074971691637</v>
       </c>
-      <c r="P22" s="184"/>
-      <c r="Q22" s="185"/>
-      <c r="R22" s="185"/>
+      <c r="P22" s="179"/>
+      <c r="Q22" s="180"/>
+      <c r="R22" s="180"/>
     </row>
     <row r="23" spans="1:18" ht="6" customHeight="1"/>
     <row r="24" spans="1:18" ht="19.5" customHeight="1">
       <c r="A24" s="114" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B24" s="115" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C24" s="81">
         <f>외기온도_시간분포!B86</f>
@@ -23570,15 +23616,15 @@
         <f>AVERAGE(C24:N24)</f>
         <v>16.775000000000002</v>
       </c>
-      <c r="P24" s="184">
+      <c r="P24" s="179">
         <f>IFERROR(SUMPRODUCT(C25:N25,C26:N26)/SUM(C25:N25),0)</f>
         <v>3.5566006959193195</v>
       </c>
-      <c r="Q24" s="185">
+      <c r="Q24" s="180">
         <f>$D$7</f>
         <v>3</v>
       </c>
-      <c r="R24" s="186" t="str">
+      <c r="R24" s="181" t="str">
         <f>IF(P24&gt;=$D$7,"✓ 달성","✗ 미달")</f>
         <v>✓ 달성</v>
       </c>
@@ -23586,7 +23632,7 @@
     <row r="25" spans="1:18" ht="19.5" customHeight="1">
       <c r="A25" s="116"/>
       <c r="B25" s="117" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C25" s="118">
         <f>MAX(0,$D$6-C24)*31</f>
@@ -23640,14 +23686,14 @@
         <f>SUM(C25:N25)</f>
         <v>1429.1</v>
       </c>
-      <c r="P25" s="184"/>
-      <c r="Q25" s="185"/>
-      <c r="R25" s="185"/>
+      <c r="P25" s="179"/>
+      <c r="Q25" s="180"/>
+      <c r="R25" s="180"/>
     </row>
     <row r="26" spans="1:18" ht="21.75" customHeight="1">
       <c r="A26" s="116"/>
       <c r="B26" s="117" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C26" s="120">
         <f t="shared" ref="C26:N26" si="3">$D$5*($D$4+273)/MAX(1,$D$4-C24)</f>
@@ -23701,36 +23747,36 @@
         <f>AVERAGE(C26:N26)</f>
         <v>4.4669458755613842</v>
       </c>
-      <c r="P26" s="184"/>
-      <c r="Q26" s="185"/>
-      <c r="R26" s="185"/>
+      <c r="P26" s="179"/>
+      <c r="Q26" s="180"/>
+      <c r="R26" s="180"/>
     </row>
     <row r="27" spans="1:18" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="E4:R4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="E5:R5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="E6:R6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E7:R7"/>
+    <mergeCell ref="A9:R9"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="Q12:Q14"/>
+    <mergeCell ref="R12:R14"/>
+    <mergeCell ref="P16:P18"/>
+    <mergeCell ref="Q16:Q18"/>
+    <mergeCell ref="R16:R18"/>
     <mergeCell ref="P20:P22"/>
     <mergeCell ref="Q20:Q22"/>
     <mergeCell ref="R20:R22"/>
     <mergeCell ref="P24:P26"/>
     <mergeCell ref="Q24:Q26"/>
     <mergeCell ref="R24:R26"/>
-    <mergeCell ref="P12:P14"/>
-    <mergeCell ref="Q12:Q14"/>
-    <mergeCell ref="R12:R14"/>
-    <mergeCell ref="P16:P18"/>
-    <mergeCell ref="Q16:Q18"/>
-    <mergeCell ref="R16:R18"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="E6:R6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E7:R7"/>
-    <mergeCell ref="A9:R9"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="E4:R4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="E5:R5"/>
   </mergeCells>
   <phoneticPr fontId="52" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -23767,101 +23813,101 @@
   <sheetData>
     <row r="3" spans="2:50">
       <c r="AK3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="2:50">
       <c r="C4" s="6" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="S4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="T4" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AK4" t="s">
+        <v>418</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>419</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>420</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>421</v>
+      </c>
+      <c r="AP4" t="s">
         <v>422</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AQ4" t="s">
         <v>423</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AR4" t="s">
         <v>424</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AS4" t="s">
         <v>425</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AT4" t="s">
         <v>426</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AU4" t="s">
         <v>427</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AV4" t="s">
         <v>428</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AW4" t="s">
         <v>429</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AX4" t="s">
         <v>430</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>431</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>432</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>433</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="5" spans="2:50">
       <c r="B5" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="H5" s="139" t="s">
+        <v>415</v>
+      </c>
+      <c r="I5" s="140" t="s">
+        <v>385</v>
+      </c>
+      <c r="J5" s="140" t="s">
+        <v>386</v>
+      </c>
+      <c r="K5" s="140" t="s">
         <v>387</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="L5" s="140" t="s">
         <v>388</v>
       </c>
-      <c r="H5" s="139" t="s">
-        <v>419</v>
-      </c>
-      <c r="I5" s="140" t="s">
+      <c r="M5" s="140" t="s">
         <v>389</v>
       </c>
-      <c r="J5" s="140" t="s">
+      <c r="N5" s="140" t="s">
         <v>390</v>
       </c>
-      <c r="K5" s="140" t="s">
+      <c r="O5" s="140" t="s">
         <v>391</v>
       </c>
-      <c r="L5" s="140" t="s">
+      <c r="P5" s="140" t="s">
         <v>392</v>
       </c>
-      <c r="M5" s="140" t="s">
+      <c r="Q5" s="140" t="s">
         <v>393</v>
       </c>
-      <c r="N5" s="140" t="s">
-        <v>394</v>
-      </c>
-      <c r="O5" s="140" t="s">
-        <v>395</v>
-      </c>
-      <c r="P5" s="140" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q5" s="140" t="s">
-        <v>397</v>
-      </c>
       <c r="R5" s="140" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="S5" s="141">
         <f>SUM(R6:R17)</f>
@@ -23876,7 +23922,7 @@
         <v>0.37782293045111248</v>
       </c>
       <c r="AK5" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AM5">
         <v>53.059104000000012</v>
@@ -23917,13 +23963,13 @@
     </row>
     <row r="6" spans="2:50">
       <c r="B6" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C6" s="122">
         <v>910</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E6">
         <v>120</v>
@@ -23972,7 +24018,7 @@
       <c r="T6" s="145"/>
       <c r="U6" s="146"/>
       <c r="AK6" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="AM6">
         <v>53.059104000000012</v>
@@ -24013,13 +24059,13 @@
     </row>
     <row r="7" spans="2:50">
       <c r="B7" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C7" s="122">
         <v>1600</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E7">
         <v>214.6</v>
@@ -24068,7 +24114,7 @@
       <c r="T7" s="145"/>
       <c r="U7" s="146"/>
       <c r="AK7" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AM7">
         <v>53.295975000000013</v>
@@ -24109,13 +24155,13 @@
     </row>
     <row r="8" spans="2:50">
       <c r="B8" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C8" s="122">
         <v>7300</v>
       </c>
       <c r="D8" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E8">
         <v>307.3</v>
@@ -24168,7 +24214,7 @@
       <c r="T8" s="145"/>
       <c r="U8" s="146"/>
       <c r="AK8" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AM8">
         <v>55.427814000000005</v>
@@ -24252,7 +24298,7 @@
       <c r="T9" s="145"/>
       <c r="U9" s="146"/>
       <c r="AK9" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AM9">
         <v>64.902654000000027</v>
@@ -24293,7 +24339,7 @@
     </row>
     <row r="10" spans="2:50">
       <c r="B10" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H10" s="143"/>
       <c r="I10">
@@ -24339,7 +24385,7 @@
       <c r="T10" s="145"/>
       <c r="U10" s="146"/>
       <c r="AK10" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AM10">
         <v>68.455719000000016</v>
@@ -24380,7 +24426,7 @@
     </row>
     <row r="11" spans="2:50">
       <c r="B11" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="H11" s="143"/>
       <c r="I11">
@@ -24426,7 +24472,7 @@
       <c r="T11" s="145"/>
       <c r="U11" s="146"/>
       <c r="AK11" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AM11">
         <v>68.455719000000016</v>
@@ -24510,7 +24556,7 @@
       <c r="T12" s="145"/>
       <c r="U12" s="146"/>
       <c r="AK12" s="9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="AM12">
         <v>66.323880000000003</v>
@@ -24551,7 +24597,7 @@
     </row>
     <row r="13" spans="2:50">
       <c r="C13" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="H13" s="143"/>
       <c r="I13">
@@ -24597,7 +24643,7 @@
       <c r="T13" s="145"/>
       <c r="U13" s="146"/>
       <c r="AK13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AM13">
         <v>58.954560000000015</v>
@@ -24638,10 +24684,10 @@
     </row>
     <row r="14" spans="2:50">
       <c r="B14" s="6" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H14" s="143"/>
       <c r="I14">
@@ -24687,7 +24733,7 @@
       <c r="T14" s="145"/>
       <c r="U14" s="146"/>
       <c r="AK14" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AM14">
         <v>56.585850000000001</v>
@@ -24728,13 +24774,13 @@
     </row>
     <row r="15" spans="2:50">
       <c r="B15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C15">
         <v>910</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E15">
         <v>120</v>
@@ -24783,7 +24829,7 @@
       <c r="T15" s="145"/>
       <c r="U15" s="146"/>
       <c r="AK15" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AM15">
         <v>59.217750000000009</v>
@@ -24824,13 +24870,13 @@
     </row>
     <row r="16" spans="2:50">
       <c r="B16" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C16" s="123">
         <v>1600</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E16">
         <v>214.6</v>
@@ -24879,7 +24925,7 @@
       <c r="T16" s="145"/>
       <c r="U16" s="146"/>
       <c r="AK16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AM16">
         <v>61.586460000000002</v>
@@ -24920,13 +24966,13 @@
     </row>
     <row r="17" spans="2:50">
       <c r="B17" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C17" s="123">
         <v>7300</v>
       </c>
       <c r="D17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E17">
         <v>307.3</v>
@@ -24979,7 +25025,7 @@
       <c r="T17" s="145"/>
       <c r="U17" s="146"/>
       <c r="AK17" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AM17">
         <v>72.114060000000023</v>
@@ -25021,34 +25067,34 @@
     <row r="18" spans="2:50">
       <c r="H18" s="143"/>
       <c r="I18" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="J18" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="N18" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="O18" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="P18" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="Q18" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="N18" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q18" s="6" t="s">
-        <v>397</v>
-      </c>
       <c r="R18" s="6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="S18" s="147">
         <f>SUM(R19:R30)</f>
@@ -25063,7 +25109,7 @@
         <v>0.44720816734708407</v>
       </c>
       <c r="AK18" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="AM18">
         <v>61.060080000000006</v>
@@ -25104,7 +25150,7 @@
     </row>
     <row r="19" spans="2:50">
       <c r="B19" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="H19" s="143"/>
       <c r="I19">
@@ -25150,7 +25196,7 @@
       <c r="T19" s="145"/>
       <c r="U19" s="146"/>
       <c r="AK19" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AM19">
         <v>76.061910000000012</v>
@@ -25191,7 +25237,7 @@
     </row>
     <row r="20" spans="2:50">
       <c r="B20" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="H20" s="143"/>
       <c r="I20">
@@ -25237,7 +25283,7 @@
       <c r="T20" s="145"/>
       <c r="U20" s="146"/>
       <c r="AK20" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AM20">
         <v>73.693200000000004</v>
@@ -25321,7 +25367,7 @@
       <c r="T21" s="145"/>
       <c r="U21" s="146"/>
       <c r="AK21" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AM21">
         <v>64.218360000000004</v>
@@ -25362,7 +25408,7 @@
     </row>
     <row r="22" spans="2:50">
       <c r="C22" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="H22" s="143"/>
       <c r="I22">
@@ -25856,34 +25902,34 @@
       </c>
       <c r="H31" s="143"/>
       <c r="I31" s="149" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="J31" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="N31" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="O31" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="P31" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="M31" s="6" t="s">
+      <c r="Q31" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="N31" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="O31" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="P31" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q31" s="6" t="s">
-        <v>397</v>
-      </c>
       <c r="R31" s="6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="S31" s="147">
         <f>SUM(R32:R43)</f>
@@ -26112,7 +26158,7 @@
     </row>
     <row r="36" spans="2:37">
       <c r="C36" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="H36" s="143"/>
       <c r="I36">
@@ -26564,34 +26610,34 @@
       </c>
       <c r="H44" s="143"/>
       <c r="I44" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="N44" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="O44" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="L44" s="6" t="s">
+      <c r="P44" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="M44" s="6" t="s">
+      <c r="Q44" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="N44" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q44" s="6" t="s">
-        <v>397</v>
-      </c>
       <c r="R44" s="6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="S44" s="147">
         <f>SUM(R45:R56)</f>
@@ -27188,37 +27234,37 @@
     </row>
     <row r="57" spans="7:21">
       <c r="H57" s="139" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="I57" s="154" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J57" s="154" t="s">
+        <v>386</v>
+      </c>
+      <c r="K57" s="154" t="s">
+        <v>387</v>
+      </c>
+      <c r="L57" s="154" t="s">
+        <v>388</v>
+      </c>
+      <c r="M57" s="154" t="s">
+        <v>389</v>
+      </c>
+      <c r="N57" s="154" t="s">
         <v>390</v>
       </c>
-      <c r="K57" s="154" t="s">
+      <c r="O57" s="154" t="s">
         <v>391</v>
       </c>
-      <c r="L57" s="154" t="s">
+      <c r="P57" s="154" t="s">
         <v>392</v>
       </c>
-      <c r="M57" s="154" t="s">
+      <c r="Q57" s="154" t="s">
         <v>393</v>
       </c>
-      <c r="N57" s="154" t="s">
-        <v>394</v>
-      </c>
-      <c r="O57" s="154" t="s">
-        <v>395</v>
-      </c>
-      <c r="P57" s="154" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q57" s="154" t="s">
-        <v>397</v>
-      </c>
       <c r="R57" s="154" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S57" s="141">
         <f>SUM(R58:R69)</f>
@@ -27778,34 +27824,34 @@
     <row r="70" spans="8:21">
       <c r="H70" s="143"/>
       <c r="I70" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="J70" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="N70" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="K70" s="6" t="s">
+      <c r="O70" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="L70" s="6" t="s">
+      <c r="P70" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="M70" s="6" t="s">
+      <c r="Q70" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="N70" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="O70" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q70" s="6" t="s">
-        <v>397</v>
-      </c>
       <c r="R70" s="6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="S70" s="147">
         <f>SUM(R71:R82)</f>
@@ -28363,34 +28409,34 @@
     <row r="83" spans="8:21">
       <c r="H83" s="143"/>
       <c r="I83" s="149" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="J83" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N83" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="O83" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L83" s="1" t="s">
+      <c r="P83" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M83" s="1" t="s">
+      <c r="Q83" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N83" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P83" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q83" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R83" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S83" s="145">
         <f>SUM(R84:R95)</f>
@@ -28924,34 +28970,34 @@
     <row r="96" spans="8:21">
       <c r="H96" s="143"/>
       <c r="I96" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J96" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N96" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="O96" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L96" s="1" t="s">
+      <c r="P96" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M96" s="1" t="s">
+      <c r="Q96" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N96" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O96" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P96" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q96" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R96" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S96" s="145">
         <f>SUM(R97:R108)</f>
@@ -29486,44 +29532,44 @@
     </row>
     <row r="109" spans="3:21">
       <c r="C109" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D109" s="1">
         <f>ROUNDUP(Sheet2!C4/D110,0)</f>
         <v>4</v>
       </c>
       <c r="H109" s="139" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I109" s="154" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J109" s="154" t="s">
+        <v>386</v>
+      </c>
+      <c r="K109" s="154" t="s">
+        <v>387</v>
+      </c>
+      <c r="L109" s="154" t="s">
+        <v>388</v>
+      </c>
+      <c r="M109" s="154" t="s">
+        <v>389</v>
+      </c>
+      <c r="N109" s="154" t="s">
         <v>390</v>
       </c>
-      <c r="K109" s="154" t="s">
+      <c r="O109" s="154" t="s">
         <v>391</v>
       </c>
-      <c r="L109" s="154" t="s">
+      <c r="P109" s="154" t="s">
         <v>392</v>
       </c>
-      <c r="M109" s="154" t="s">
+      <c r="Q109" s="154" t="s">
         <v>393</v>
       </c>
-      <c r="N109" s="154" t="s">
-        <v>394</v>
-      </c>
-      <c r="O109" s="154" t="s">
-        <v>395</v>
-      </c>
-      <c r="P109" s="154" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q109" s="154" t="s">
-        <v>397</v>
-      </c>
       <c r="R109" s="154" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S109" s="157">
         <f>SUM(R110:R121)</f>
@@ -29540,7 +29586,7 @@
     </row>
     <row r="110" spans="3:21">
       <c r="C110" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D110" s="1">
         <v>3</v>
@@ -29730,16 +29776,16 @@
     </row>
     <row r="114" spans="3:21">
       <c r="C114" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E114" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F114" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H114" s="143"/>
       <c r="I114">
@@ -29785,16 +29831,16 @@
     </row>
     <row r="115" spans="3:21">
       <c r="C115" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E115" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F115" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H115" s="143"/>
       <c r="I115">
@@ -29840,10 +29886,10 @@
     </row>
     <row r="116" spans="3:21">
       <c r="D116" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E116" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="H116" s="143"/>
       <c r="I116">
@@ -30105,34 +30151,34 @@
     <row r="122" spans="3:21">
       <c r="H122" s="143"/>
       <c r="I122" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="J122" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N122" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K122" s="1" t="s">
+      <c r="O122" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L122" s="1" t="s">
+      <c r="P122" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M122" s="1" t="s">
+      <c r="Q122" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N122" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O122" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P122" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q122" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R122" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S122" s="145">
         <f>SUM(R123:R134)</f>
@@ -30666,34 +30712,34 @@
     <row r="135" spans="8:21">
       <c r="H135" s="143"/>
       <c r="I135" s="149" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="J135" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N135" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K135" s="1" t="s">
+      <c r="O135" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L135" s="1" t="s">
+      <c r="P135" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M135" s="1" t="s">
+      <c r="Q135" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N135" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O135" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P135" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q135" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R135" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S135" s="145">
         <f>SUM(R136:R147)</f>
@@ -31227,34 +31273,34 @@
     <row r="148" spans="8:21">
       <c r="H148" s="143"/>
       <c r="I148" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J148" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M148" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N148" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K148" s="1" t="s">
+      <c r="O148" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L148" s="1" t="s">
+      <c r="P148" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M148" s="1" t="s">
+      <c r="Q148" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N148" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O148" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P148" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q148" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R148" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S148" s="145">
         <f>SUM(R149:R160)</f>
@@ -31789,40 +31835,40 @@
     </row>
     <row r="161" spans="2:21">
       <c r="B161" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="H161" s="139" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="I161" s="154" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J161" s="154" t="s">
+        <v>386</v>
+      </c>
+      <c r="K161" s="154" t="s">
+        <v>387</v>
+      </c>
+      <c r="L161" s="154" t="s">
+        <v>388</v>
+      </c>
+      <c r="M161" s="154" t="s">
+        <v>389</v>
+      </c>
+      <c r="N161" s="154" t="s">
         <v>390</v>
       </c>
-      <c r="K161" s="154" t="s">
+      <c r="O161" s="154" t="s">
         <v>391</v>
       </c>
-      <c r="L161" s="154" t="s">
+      <c r="P161" s="154" t="s">
         <v>392</v>
       </c>
-      <c r="M161" s="154" t="s">
+      <c r="Q161" s="154" t="s">
         <v>393</v>
       </c>
-      <c r="N161" s="154" t="s">
-        <v>394</v>
-      </c>
-      <c r="O161" s="154" t="s">
-        <v>395</v>
-      </c>
-      <c r="P161" s="154" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q161" s="154" t="s">
-        <v>397</v>
-      </c>
       <c r="R161" s="154" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S161" s="157">
         <f>SUM(R162:R173)</f>
@@ -31839,7 +31885,7 @@
     </row>
     <row r="162" spans="2:21">
       <c r="B162" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="H162" s="143"/>
       <c r="I162">
@@ -31885,7 +31931,7 @@
     </row>
     <row r="163" spans="2:21">
       <c r="B163" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H163" s="143"/>
       <c r="I163">
@@ -32017,13 +32063,13 @@
     </row>
     <row r="166" spans="2:21">
       <c r="B166" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C166" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H166" s="143"/>
       <c r="I166">
@@ -32069,7 +32115,7 @@
     </row>
     <row r="167" spans="2:21">
       <c r="B167" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C167">
         <v>125.8</v>
@@ -32121,7 +32167,7 @@
     </row>
     <row r="168" spans="2:21">
       <c r="B168" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C168">
         <v>153.80000000000001</v>
@@ -32173,7 +32219,7 @@
     </row>
     <row r="169" spans="2:21">
       <c r="B169" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C169">
         <v>172.4</v>
@@ -32225,7 +32271,7 @@
     </row>
     <row r="170" spans="2:21">
       <c r="B170" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C170" s="123">
         <v>4310</v>
@@ -32360,7 +32406,7 @@
     </row>
     <row r="173" spans="2:21">
       <c r="B173" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="H173" s="143"/>
       <c r="I173">
@@ -32406,38 +32452,38 @@
     </row>
     <row r="174" spans="2:21">
       <c r="B174" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="H174" s="143"/>
       <c r="I174" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="J174" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K174" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L174" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M174" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N174" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K174" s="1" t="s">
+      <c r="O174" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L174" s="1" t="s">
+      <c r="P174" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M174" s="1" t="s">
+      <c r="Q174" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N174" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O174" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P174" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q174" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R174" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S174" s="145">
         <f>SUM(R175:R186)</f>
@@ -32454,7 +32500,7 @@
     </row>
     <row r="175" spans="2:21">
       <c r="B175" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H175" s="143"/>
       <c r="I175">
@@ -32985,34 +33031,34 @@
       <c r="B187" s="133"/>
       <c r="H187" s="143"/>
       <c r="I187" s="149" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="J187" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K187" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L187" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M187" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N187" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K187" s="1" t="s">
+      <c r="O187" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L187" s="1" t="s">
+      <c r="P187" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M187" s="1" t="s">
+      <c r="Q187" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N187" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O187" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P187" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q187" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R187" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S187" s="145">
         <f>SUM(R188:R199)</f>
@@ -33547,34 +33593,34 @@
     <row r="200" spans="8:21">
       <c r="H200" s="143"/>
       <c r="I200" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J200" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K200" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L200" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M200" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N200" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K200" s="1" t="s">
+      <c r="O200" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L200" s="1" t="s">
+      <c r="P200" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M200" s="1" t="s">
+      <c r="Q200" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N200" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O200" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P200" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q200" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R200" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S200" s="145">
         <f>SUM(R201:R212)</f>
@@ -34109,37 +34155,37 @@
     </row>
     <row r="213" spans="8:21">
       <c r="H213" s="139" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="I213" s="154" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J213" s="154" t="s">
+        <v>386</v>
+      </c>
+      <c r="K213" s="154" t="s">
+        <v>387</v>
+      </c>
+      <c r="L213" s="154" t="s">
+        <v>388</v>
+      </c>
+      <c r="M213" s="154" t="s">
+        <v>389</v>
+      </c>
+      <c r="N213" s="154" t="s">
         <v>390</v>
       </c>
-      <c r="K213" s="154" t="s">
+      <c r="O213" s="154" t="s">
         <v>391</v>
       </c>
-      <c r="L213" s="154" t="s">
+      <c r="P213" s="154" t="s">
         <v>392</v>
       </c>
-      <c r="M213" s="154" t="s">
+      <c r="Q213" s="154" t="s">
         <v>393</v>
       </c>
-      <c r="N213" s="154" t="s">
-        <v>394</v>
-      </c>
-      <c r="O213" s="154" t="s">
-        <v>395</v>
-      </c>
-      <c r="P213" s="154" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q213" s="154" t="s">
-        <v>397</v>
-      </c>
       <c r="R213" s="154" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S213" s="157">
         <f>SUM(R214:R225)</f>
@@ -34673,34 +34719,34 @@
     <row r="226" spans="8:21">
       <c r="H226" s="143"/>
       <c r="I226" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="J226" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K226" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L226" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M226" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N226" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K226" s="1" t="s">
+      <c r="O226" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L226" s="1" t="s">
+      <c r="P226" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M226" s="1" t="s">
+      <c r="Q226" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N226" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O226" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P226" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q226" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R226" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S226" s="145">
         <f>SUM(R227:R238)</f>
@@ -35234,34 +35280,34 @@
     <row r="239" spans="8:21">
       <c r="H239" s="143"/>
       <c r="I239" s="149" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="J239" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K239" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L239" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M239" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N239" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K239" s="1" t="s">
+      <c r="O239" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L239" s="1" t="s">
+      <c r="P239" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M239" s="1" t="s">
+      <c r="Q239" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N239" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O239" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P239" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q239" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R239" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S239" s="145">
         <f>SUM(R240:R251)</f>
@@ -35795,34 +35841,34 @@
     <row r="252" spans="8:21">
       <c r="H252" s="143"/>
       <c r="I252" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J252" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K252" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L252" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M252" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N252" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K252" s="1" t="s">
+      <c r="O252" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="L252" s="1" t="s">
+      <c r="P252" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="M252" s="1" t="s">
+      <c r="Q252" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="N252" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O252" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="P252" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q252" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="R252" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="S252" s="145">
         <f>SUM(R253:R264)</f>

--- a/전기요금완료본.xlsx
+++ b/전기요금완료본.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D5B722-A3DA-4826-B658-62BF01225AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
